--- a/seo-texts/group-gap-candidates.xlsx
+++ b/seo-texts/group-gap-candidates.xlsx
@@ -675,21 +675,21 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Напряжение питания, В</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>738</v>
+        <v>693</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -705,26 +705,26 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Температурный режим</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>До -40°C</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>693</v>
+        <v>614</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -740,26 +740,26 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Температурный режим</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>До -40°C</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>614</v>
+        <v>574</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -780,21 +780,21 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>574</v>
+        <v>494</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Тип компрессора</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>ctype</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>поршневой</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -845,26 +845,26 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Тип компрессора</t>
+          <t>Температурный режим</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>ctype</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>поршневой</t>
+          <t>До -20°C</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>482</v>
+        <v>363</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -880,26 +880,26 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Температурный режим</t>
+          <t>Назначение</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>До -20°C</t>
+          <t>Для медицины</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -930,11 +930,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Для медицины</t>
+          <t>Для буровых установок</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -950,26 +950,26 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Назначение</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Для буровых установок</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -985,26 +985,26 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1035,11 +1035,11 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1055,26 +1055,26 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Товарная группа (1С)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>tgroup</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Генераторы азота</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1090,26 +1090,26 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Назначение</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Генераторы азота</t>
+          <t>Для лазерной резки</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1125,26 +1125,26 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Назначение</t>
+          <t>Степень защиты двигателя</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>ipclass</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Для лазерной резки</t>
+          <t>IP65</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Степень защиты двигателя</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ipclass</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>IP65</t>
+          <t>Yuchai</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1195,26 +1195,26 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Напряжение питания, В</t>
+          <t>Малошумное исполнение</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>quiet</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>380/660</t>
+          <t>да</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1230,26 +1230,26 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Yuchai</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1265,26 +1265,26 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Малошумное исполнение</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>quiet</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1300,26 +1300,26 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Тип охлаждения</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>cooling</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>водяное</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1340,21 +1340,21 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Тип компрессора</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>ctype</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>шестеренчатый</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1370,26 +1370,26 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Тип охлаждения</t>
+          <t>Тип компрессора</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>cooling</t>
+          <t>ctype</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>водяное</t>
+          <t>поршневой безмасляный</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1405,26 +1405,26 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Тип компрессора</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>ctype</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>шестеренчатый</t>
+          <t>Isuzu</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Тип компрессора</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>ctype</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>поршневой безмасляный</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1475,26 +1475,26 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Напряжение питания, В</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Isuzu</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Напряжение питания, В</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>660/1140</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1550,21 +1550,21 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Напряжение питания, В</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Напряжение питания, В</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>660/1140</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -1665,11 +1665,11 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -1735,11 +1735,11 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -1760,21 +1760,21 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -1790,26 +1790,26 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Степень защиты двигателя</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>ipclass</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>IP66</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -1860,26 +1860,26 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Степень защиты двигателя</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ipclass</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>IP66</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -1965,26 +1965,26 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Объём ресивера, л</t>
+          <t>Товарная группа (1С)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>tgroup</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Компрессоры центробежные</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2035,26 +2035,26 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Объём ресивера, л</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Компрессоры центробежные</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2085,11 +2085,11 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2120,11 +2120,11 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2133,70 +2133,70 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>пробел в фасете</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Объём ресивера, л</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>recv</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>новый фасет</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Серия</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>TIDY</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>297</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>пробел в фасете</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Объём ресивера, л</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>recv</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>новый фасет</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Серия</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>ВК</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>273</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2225,11 +2225,11 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>TIDY</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F49" s="9" t="n">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -2260,11 +2260,11 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>ВК</t>
+          <t>SPINN</t>
         </is>
       </c>
       <c r="F50" s="9" t="n">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -2295,11 +2295,11 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="F51" s="9" t="n">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>SPINN</t>
+          <t>INVERSYS PLUS</t>
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -2365,11 +2365,11 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>EKO</t>
         </is>
       </c>
       <c r="F53" s="9" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>INVERSYS PLUS</t>
+          <t>DMD</t>
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>EKO</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -2470,11 +2470,11 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>DMD</t>
+          <t>COMBI</t>
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -2505,11 +2505,11 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>FORMULA</t>
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -2540,11 +2540,11 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>COMBI</t>
+          <t>FORTIUS</t>
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>FORMULA</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="F59" s="9" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -2610,11 +2610,11 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>FORTIUS</t>
+          <t>ZT/ZR</t>
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -2645,11 +2645,11 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>LENTO</t>
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -2680,11 +2680,11 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>ZT/ZR</t>
+          <t>G</t>
         </is>
       </c>
       <c r="F62" s="9" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -2715,11 +2715,11 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>LENTO</t>
+          <t>K-MAX</t>
         </is>
       </c>
       <c r="F63" s="9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -2750,11 +2750,11 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>MICRON</t>
         </is>
       </c>
       <c r="F64" s="9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
@@ -2785,11 +2785,11 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>K-MAX</t>
+          <t>DVK D</t>
         </is>
       </c>
       <c r="F65" s="9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -2820,11 +2820,11 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>MICRON</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F66" s="9" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
@@ -2855,11 +2855,11 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>DVK D</t>
+          <t>VEGA 2 поколение CF</t>
         </is>
       </c>
       <c r="F67" s="9" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
@@ -2890,11 +2890,11 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F68" s="9" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
@@ -2925,11 +2925,11 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>VEGA 2 поколение CF</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="F69" s="9" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F70" s="9" t="n">
@@ -2995,11 +2995,11 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>DVK</t>
         </is>
       </c>
       <c r="F71" s="9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3030,11 +3030,11 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="F72" s="9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>DVK</t>
+          <t>WIS</t>
         </is>
       </c>
       <c r="F73" s="9" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
@@ -3100,11 +3100,11 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>Т</t>
         </is>
       </c>
       <c r="F74" s="9" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
@@ -3135,11 +3135,11 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>WIS</t>
+          <t>GA+</t>
         </is>
       </c>
       <c r="F75" s="9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
@@ -3170,11 +3170,11 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Т</t>
+          <t>Eagle-D VSD</t>
         </is>
       </c>
       <c r="F76" s="9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -3205,11 +3205,11 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>GA+</t>
+          <t>TAURUS</t>
         </is>
       </c>
       <c r="F77" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
@@ -3240,11 +3240,11 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Eagle-D VSD</t>
+          <t>VARIABLE-XP</t>
         </is>
       </c>
       <c r="F78" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
@@ -3275,11 +3275,11 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>TAURUS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F79" s="9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
@@ -3310,11 +3310,11 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>VARIABLE-XP</t>
+          <t>MICRO</t>
         </is>
       </c>
       <c r="F80" s="9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
@@ -3345,11 +3345,11 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="F81" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>MICRO</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="F82" s="9" t="n">
@@ -3415,11 +3415,11 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F83" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -3450,11 +3450,11 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Eagle-D WC</t>
         </is>
       </c>
       <c r="F84" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>BELT</t>
         </is>
       </c>
       <c r="F85" s="9" t="n">
@@ -3520,11 +3520,11 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Eagle-D WC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F86" s="9" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>BELT</t>
+          <t>GEAR</t>
         </is>
       </c>
       <c r="F87" s="9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
@@ -3590,11 +3590,11 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>А</t>
         </is>
       </c>
       <c r="F88" s="9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
@@ -3625,11 +3625,11 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>GEAR</t>
+          <t>ALTAIR</t>
         </is>
       </c>
       <c r="F89" s="9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
@@ -3660,11 +3660,11 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Eagle-DW VSD</t>
         </is>
       </c>
       <c r="F90" s="9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
@@ -3695,11 +3695,11 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>ALTAIR</t>
+          <t>СD</t>
         </is>
       </c>
       <c r="F91" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
@@ -3730,11 +3730,11 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Eagle-DW VSD</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F92" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
@@ -3765,11 +3765,11 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>СD</t>
+          <t>Borey</t>
         </is>
       </c>
       <c r="F93" s="9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
@@ -3800,11 +3800,11 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>VISION</t>
         </is>
       </c>
       <c r="F94" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
@@ -3835,11 +3835,11 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Borey</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="F95" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
@@ -3870,11 +3870,11 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>VISION</t>
+          <t>V-DRIVE</t>
         </is>
       </c>
       <c r="F96" s="9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
@@ -3905,11 +3905,11 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>VARIABLE</t>
         </is>
       </c>
       <c r="F97" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>V-DRIVE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F98" s="9" t="n">
@@ -3975,11 +3975,11 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>VARIABLE</t>
+          <t>GENESIS</t>
         </is>
       </c>
       <c r="F99" s="9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
@@ -4010,11 +4010,11 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="F100" s="9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>GENESIS</t>
+          <t>КМ</t>
         </is>
       </c>
       <c r="F101" s="9" t="n">
@@ -4080,11 +4080,11 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>AX BD</t>
         </is>
       </c>
       <c r="F102" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>КМ</t>
+          <t>AX BD DRY</t>
         </is>
       </c>
       <c r="F103" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
@@ -4150,11 +4150,11 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>AX BD</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="F104" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>AX BD DRY</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="F105" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
@@ -4220,11 +4220,11 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>AQ</t>
         </is>
       </c>
       <c r="F106" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="F107" s="9" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>AQ</t>
+          <t>DPR-D</t>
         </is>
       </c>
       <c r="F108" s="9" t="n">
@@ -4325,11 +4325,11 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>AV</t>
+          <t>К</t>
         </is>
       </c>
       <c r="F109" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
@@ -4360,11 +4360,11 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>DPR-D</t>
+          <t>КТ</t>
         </is>
       </c>
       <c r="F110" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>К</t>
+          <t>GA VSD plus</t>
         </is>
       </c>
       <c r="F111" s="9" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>КТ</t>
+          <t>DBK</t>
         </is>
       </c>
       <c r="F112" s="9" t="n">
@@ -4465,11 +4465,11 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>GA VSD plus</t>
+          <t>ARD</t>
         </is>
       </c>
       <c r="F113" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
@@ -4500,11 +4500,11 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>DBK</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F114" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>ARD</t>
+          <t>MIG</t>
         </is>
       </c>
       <c r="F115" s="9" t="n">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>SPDВ</t>
         </is>
       </c>
       <c r="F116" s="9" t="n">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>MIG</t>
+          <t>GX</t>
         </is>
       </c>
       <c r="F117" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
@@ -4640,11 +4640,11 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>SPDВ</t>
+          <t>POLARIS-W (водяное охлаждение)</t>
         </is>
       </c>
       <c r="F118" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>GX</t>
+          <t>PETMASTER</t>
         </is>
       </c>
       <c r="F119" s="9" t="n">
@@ -4710,11 +4710,11 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>POLARIS-W (водяное охлаждение)</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="F120" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
@@ -4745,11 +4745,11 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>PETMASTER</t>
+          <t>KPR</t>
         </is>
       </c>
       <c r="F121" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
@@ -4780,11 +4780,11 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>KTPR</t>
         </is>
       </c>
       <c r="F122" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>KPR</t>
+          <t>Typhoon</t>
         </is>
       </c>
       <c r="F123" s="9" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>KTPR</t>
+          <t>PET PLUS</t>
         </is>
       </c>
       <c r="F124" s="9" t="n">
@@ -4885,11 +4885,11 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Typhoon</t>
+          <t>POLARIS</t>
         </is>
       </c>
       <c r="F125" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
@@ -4898,70 +4898,70 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>новый фасет</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Серия</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t>PET PLUS</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>Винтовой блок</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Baosi</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>2339</v>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
         <is>
           <t>новый фасет</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>Серия</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t>POLARIS</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>Винтовой блок</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Hanbell AB</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>871</v>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -4990,11 +4990,11 @@
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>Baosi</t>
+          <t>RotorComp</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>2339</v>
+        <v>786</v>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
@@ -5025,11 +5025,11 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Hanbell AB</t>
+          <t>Atlas Copco</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>871</v>
+        <v>754</v>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
@@ -5060,11 +5060,11 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>RotorComp</t>
+          <t>Atlas Copco C</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>786</v>
+        <v>730</v>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
@@ -5095,11 +5095,11 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Atlas Copco</t>
+          <t>АРМ</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>754</v>
+        <v>709</v>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
@@ -5130,11 +5130,11 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Atlas Copco C</t>
+          <t>ASU</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>730</v>
+        <v>686</v>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
@@ -5165,11 +5165,11 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>АРМ</t>
+          <t>Almig</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>709</v>
+        <v>577</v>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
@@ -5200,11 +5200,11 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>ASU</t>
+          <t>Aerzener</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>686</v>
+        <v>534</v>
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
@@ -5235,11 +5235,11 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Almig</t>
+          <t>Hanbell AC</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>577</v>
+        <v>505</v>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
@@ -5270,11 +5270,11 @@
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>Aerzener</t>
+          <t>Hanbell</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>534</v>
+        <v>492</v>
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Hanbell AC</t>
+          <t>Hanbell ABD</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
@@ -5340,11 +5340,11 @@
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>Hanbell</t>
+          <t>Atmos</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
@@ -5375,11 +5375,11 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Hanbell ABD</t>
+          <t>SKK</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>462</v>
+        <v>361</v>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
@@ -5410,11 +5410,11 @@
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>Atmos</t>
+          <t>FINI</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
@@ -5445,11 +5445,11 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>SKK</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
@@ -5480,11 +5480,11 @@
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>FINI</t>
+          <t>Remeza</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
@@ -5515,11 +5515,11 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Jiuyi</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
@@ -5550,11 +5550,11 @@
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>Remeza</t>
+          <t>Hanbell AA</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
@@ -5585,11 +5585,11 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Jiuyi</t>
+          <t>Termomeccanica</t>
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
@@ -5620,11 +5620,11 @@
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>Hanbell AA</t>
+          <t>GHH Rand</t>
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
@@ -5640,26 +5640,26 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Termomeccanica</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
@@ -5675,26 +5675,26 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>GHH Rand</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
@@ -5725,11 +5725,11 @@
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="F149" s="13" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G149" s="10" t="inlineStr">
         <is>
@@ -5760,11 +5760,11 @@
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>280</t>
         </is>
       </c>
       <c r="F150" s="13" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
@@ -5780,26 +5780,26 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>Niemann</t>
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
@@ -5820,21 +5820,21 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
@@ -5850,26 +5850,26 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>Niemann</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F153" s="13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
@@ -5900,11 +5900,11 @@
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F154" s="13" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
@@ -5925,21 +5925,21 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="F155" s="13" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
@@ -5970,11 +5970,11 @@
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F156" s="13" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
@@ -5995,21 +5995,21 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
@@ -6025,26 +6025,26 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="F158" s="13" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
@@ -6065,21 +6065,21 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F159" s="13" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
@@ -6110,11 +6110,11 @@
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>Comprag</t>
         </is>
       </c>
       <c r="F160" s="13" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
@@ -6145,11 +6145,11 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
@@ -6165,26 +6165,26 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>Comprag</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G162" s="10" t="inlineStr">
         <is>
@@ -6205,21 +6205,21 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="F163" s="13" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G163" s="10" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F164" s="13" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
@@ -6275,21 +6275,21 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="F165" s="13" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G166" s="10" t="inlineStr">
         <is>
@@ -6355,11 +6355,11 @@
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G167" s="10" t="inlineStr">
         <is>
@@ -6380,17 +6380,17 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="F168" s="13" t="n">
@@ -6425,11 +6425,11 @@
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
@@ -6460,11 +6460,11 @@
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="F170" s="13" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G170" s="10" t="inlineStr">
         <is>
@@ -6495,11 +6495,11 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="F171" s="13" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
@@ -6520,21 +6520,21 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>10,5</t>
         </is>
       </c>
       <c r="F172" s="13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G172" s="10" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F173" s="13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G173" s="10" t="inlineStr">
         <is>
@@ -6590,21 +6590,21 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="F174" s="13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G174" s="10" t="inlineStr">
         <is>
@@ -6620,26 +6620,26 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Ironmac</t>
         </is>
       </c>
       <c r="F175" s="13" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G175" s="10" t="inlineStr">
         <is>
@@ -6670,11 +6670,11 @@
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F176" s="13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G176" s="10" t="inlineStr">
         <is>
@@ -6690,26 +6690,26 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>Ironmac</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="F177" s="13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G177" s="10" t="inlineStr">
         <is>
@@ -6725,26 +6725,26 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>Kubota</t>
         </is>
       </c>
       <c r="F178" s="13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G178" s="10" t="inlineStr">
         <is>
@@ -6760,26 +6760,26 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>AIPU</t>
         </is>
       </c>
       <c r="F179" s="13" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
@@ -6795,26 +6795,26 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>Kubota</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F180" s="13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G180" s="10" t="inlineStr">
         <is>
@@ -6830,26 +6830,26 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>AIPU</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="F181" s="13" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
@@ -6870,21 +6870,21 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="F182" s="13" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
@@ -6915,11 +6915,11 @@
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="F183" s="13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G183" s="10" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F184" s="13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G184" s="10" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="F185" s="13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
@@ -7005,26 +7005,26 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="F186" s="13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
@@ -7045,21 +7045,21 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="F187" s="13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
@@ -7075,26 +7075,26 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="F188" s="13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
@@ -7115,21 +7115,21 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="F189" s="13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
@@ -7145,26 +7145,26 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>HDHJ</t>
         </is>
       </c>
       <c r="F190" s="13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
@@ -7180,26 +7180,26 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>Atlas Copco S</t>
         </is>
       </c>
       <c r="F191" s="13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>HDHJ</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="F192" s="13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G192" s="10" t="inlineStr">
         <is>
@@ -7250,26 +7250,26 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
         <is>
-          <t>Atlas Copco S</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="F193" s="13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
@@ -7290,21 +7290,21 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="F194" s="13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
@@ -7325,21 +7325,21 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr">
         <is>
-          <t>32000</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F195" s="13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G195" s="10" t="inlineStr">
         <is>
@@ -7355,26 +7355,26 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F196" s="13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G196" s="10" t="inlineStr">
         <is>
@@ -7395,21 +7395,21 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="F197" s="13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="F198" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G198" s="10" t="inlineStr">
         <is>
@@ -7475,11 +7475,11 @@
       </c>
       <c r="E199" s="12" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="F199" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G199" s="10" t="inlineStr">
         <is>
@@ -7500,21 +7500,21 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F200" s="13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G200" s="10" t="inlineStr">
         <is>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="E201" s="12" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="F201" s="13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G201" s="10" t="inlineStr">
         <is>
@@ -7580,11 +7580,11 @@
       </c>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F202" s="13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G202" s="10" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E203" s="12" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F203" s="13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
@@ -7635,26 +7635,26 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Винтовой блок</t>
         </is>
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>block</t>
         </is>
       </c>
       <c r="E204" s="12" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>Xinlei</t>
         </is>
       </c>
       <c r="F204" s="13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G204" s="10" t="inlineStr">
         <is>
@@ -7675,21 +7675,21 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F205" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
@@ -7705,22 +7705,22 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Винтовой блок</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D206" s="11" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E206" s="12" t="inlineStr">
         <is>
-          <t>Xinlei</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F206" s="13" t="n">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="E207" s="12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="F207" s="13" t="n">
@@ -7780,21 +7780,21 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D208" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F208" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G208" s="10" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D209" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E209" s="12" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F209" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G209" s="10" t="inlineStr">
         <is>
@@ -7850,17 +7850,17 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D210" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E210" s="12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F210" s="13" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E211" s="12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="F211" s="13" t="n">
@@ -7920,21 +7920,21 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E212" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F212" s="13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G212" s="10" t="inlineStr">
         <is>
@@ -7950,26 +7950,26 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E213" s="12" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>Yunnei</t>
         </is>
       </c>
       <c r="F213" s="13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
@@ -7990,21 +7990,21 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D214" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="F214" s="13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G214" s="10" t="inlineStr">
         <is>
@@ -8020,26 +8020,26 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E215" s="12" t="inlineStr">
         <is>
-          <t>Yunnei</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="F215" s="13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G215" s="10" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D216" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F216" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G216" s="10" t="inlineStr">
         <is>
@@ -8105,11 +8105,11 @@
       </c>
       <c r="E217" s="12" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>52000</t>
         </is>
       </c>
       <c r="F217" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G217" s="10" t="inlineStr">
         <is>
@@ -8125,26 +8125,26 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D218" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Perkins</t>
         </is>
       </c>
       <c r="F218" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
@@ -8165,21 +8165,21 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E219" s="12" t="inlineStr">
         <is>
-          <t>52000</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F219" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G219" s="10" t="inlineStr">
         <is>
@@ -8195,22 +8195,22 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D220" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E220" s="12" t="inlineStr">
         <is>
-          <t>Perkins</t>
+          <t>39000</t>
         </is>
       </c>
       <c r="F220" s="13" t="n">
@@ -8235,21 +8235,21 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D221" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E221" s="12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>48000</t>
         </is>
       </c>
       <c r="F221" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
@@ -8265,26 +8265,26 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D222" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E222" s="12" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>Xichai</t>
         </is>
       </c>
       <c r="F222" s="13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G222" s="10" t="inlineStr">
         <is>
@@ -8300,26 +8300,26 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D223" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E223" s="12" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>Deutz</t>
         </is>
       </c>
       <c r="F223" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G223" s="10" t="inlineStr">
         <is>
@@ -8335,22 +8335,22 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D224" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E224" s="12" t="inlineStr">
         <is>
-          <t>Xichai</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="F224" s="13" t="n">
@@ -8385,11 +8385,11 @@
       </c>
       <c r="E225" s="12" t="inlineStr">
         <is>
-          <t>Deutz</t>
+          <t>Faw</t>
         </is>
       </c>
       <c r="F225" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
@@ -8405,26 +8405,26 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>пробел в фасете</t>
+          <t>новый фасет</t>
         </is>
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>Производительность, л/мин</t>
+          <t>Производитель ДВС</t>
         </is>
       </c>
       <c r="D226" s="11" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="E226" s="12" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>Yushai</t>
         </is>
       </c>
       <c r="F226" s="13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
@@ -8440,26 +8440,26 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D227" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E227" s="12" t="inlineStr">
         <is>
-          <t>Faw</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F227" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G227" s="10" t="inlineStr">
         <is>
@@ -8490,11 +8490,11 @@
       </c>
       <c r="E228" s="12" t="inlineStr">
         <is>
-          <t>Yushai</t>
+          <t>Jiangtian</t>
         </is>
       </c>
       <c r="F228" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G228" s="10" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Рабочее давление, бар</t>
         </is>
       </c>
       <c r="D229" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>press</t>
         </is>
       </c>
       <c r="E229" s="12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F229" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G229" s="10" t="inlineStr">
         <is>
@@ -8545,22 +8545,22 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Производитель ДВС</t>
+          <t>Мощность, кВт</t>
         </is>
       </c>
       <c r="D230" s="11" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>power</t>
         </is>
       </c>
       <c r="E230" s="12" t="inlineStr">
         <is>
-          <t>Jiangtian</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F230" s="13" t="n">
@@ -8585,17 +8585,17 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Рабочее давление, бар</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D231" s="11" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E231" s="12" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="F231" s="13" t="n">
@@ -8630,11 +8630,11 @@
       </c>
       <c r="E232" s="12" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F232" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G232" s="10" t="inlineStr">
         <is>
@@ -8665,11 +8665,11 @@
       </c>
       <c r="E233" s="12" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="F233" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G233" s="10" t="inlineStr">
         <is>
@@ -8690,17 +8690,17 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>Мощность, кВт</t>
+          <t>Производительность, л/мин</t>
         </is>
       </c>
       <c r="D234" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="E234" s="12" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="F234" s="13" t="n">
@@ -8713,70 +8713,70 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B235" s="11" t="inlineStr">
-        <is>
-          <t>пробел в фасете</t>
-        </is>
-      </c>
-      <c r="C235" s="11" t="inlineStr">
-        <is>
-          <t>Производительность, л/мин</t>
-        </is>
-      </c>
-      <c r="D235" s="11" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="E235" s="12" t="inlineStr">
-        <is>
-          <t>46000</t>
-        </is>
-      </c>
-      <c r="F235" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G235" s="10" t="inlineStr">
+      <c r="A235" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B235" s="15" t="inlineStr">
+        <is>
+          <t>новый фасет</t>
+        </is>
+      </c>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>Товарная группа (1С)</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>tgroup</t>
+        </is>
+      </c>
+      <c r="E235" s="16" t="inlineStr">
+        <is>
+          <t>Компрессоры масляные 1 ст (7-15 бар)</t>
+        </is>
+      </c>
+      <c r="F235" s="17" t="n">
+        <v>6322</v>
+      </c>
+      <c r="G235" s="14" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B236" s="11" t="inlineStr">
-        <is>
-          <t>пробел в фасете</t>
-        </is>
-      </c>
-      <c r="C236" s="11" t="inlineStr">
-        <is>
-          <t>Производительность, л/мин</t>
-        </is>
-      </c>
-      <c r="D236" s="11" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="E236" s="12" t="inlineStr">
-        <is>
-          <t>44000</t>
-        </is>
-      </c>
-      <c r="F236" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G236" s="10" t="inlineStr">
+      <c r="A236" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B236" s="15" t="inlineStr">
+        <is>
+          <t>новый фасет</t>
+        </is>
+      </c>
+      <c r="C236" s="15" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="D236" s="15" t="inlineStr">
+        <is>
+          <t>warranty</t>
+        </is>
+      </c>
+      <c r="E236" s="16" t="inlineStr">
+        <is>
+          <t>2 года</t>
+        </is>
+      </c>
+      <c r="F236" s="17" t="n">
+        <v>5789</v>
+      </c>
+      <c r="G236" s="14" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -8795,21 +8795,21 @@
       </c>
       <c r="C237" s="15" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Гарантия</t>
         </is>
       </c>
       <c r="D237" s="15" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>warranty</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры масляные 1 ст (7-15 бар)</t>
+          <t>3 года</t>
         </is>
       </c>
       <c r="F237" s="17" t="n">
-        <v>6322</v>
+        <v>1624</v>
       </c>
       <c r="G237" s="14" t="inlineStr">
         <is>
@@ -8830,21 +8830,21 @@
       </c>
       <c r="C238" s="15" t="inlineStr">
         <is>
-          <t>Гарантия</t>
+          <t>Товарная группа (1С)</t>
         </is>
       </c>
       <c r="D238" s="15" t="inlineStr">
         <is>
-          <t>warranty</t>
+          <t>tgroup</t>
         </is>
       </c>
       <c r="E238" s="16" t="inlineStr">
         <is>
-          <t>2 года</t>
+          <t>Компрессоры безмаслянные винтовые</t>
         </is>
       </c>
       <c r="F238" s="17" t="n">
-        <v>5789</v>
+        <v>1478</v>
       </c>
       <c r="G238" s="14" t="inlineStr">
         <is>
@@ -8865,21 +8865,21 @@
       </c>
       <c r="C239" s="15" t="inlineStr">
         <is>
-          <t>Гарантия</t>
+          <t>Тип охлаждения</t>
         </is>
       </c>
       <c r="D239" s="15" t="inlineStr">
         <is>
-          <t>warranty</t>
+          <t>cooling</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>3 года</t>
+          <t>воздушное</t>
         </is>
       </c>
       <c r="F239" s="17" t="n">
-        <v>1624</v>
+        <v>1245</v>
       </c>
       <c r="G239" s="14" t="inlineStr">
         <is>
@@ -8910,11 +8910,11 @@
       </c>
       <c r="E240" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры безмаслянные винтовые</t>
+          <t>Компрессоры дизельные</t>
         </is>
       </c>
       <c r="F240" s="17" t="n">
-        <v>1478</v>
+        <v>1013</v>
       </c>
       <c r="G240" s="14" t="inlineStr">
         <is>
@@ -8935,21 +8935,21 @@
       </c>
       <c r="C241" s="15" t="inlineStr">
         <is>
-          <t>Тип охлаждения</t>
+          <t>Товарная группа (1С)</t>
         </is>
       </c>
       <c r="D241" s="15" t="inlineStr">
         <is>
-          <t>cooling</t>
+          <t>tgroup</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>воздушное</t>
+          <t>Компрессоры масляные 2 ст.</t>
         </is>
       </c>
       <c r="F241" s="17" t="n">
-        <v>1245</v>
+        <v>987</v>
       </c>
       <c r="G241" s="14" t="inlineStr">
         <is>
@@ -8965,26 +8965,26 @@
       </c>
       <c r="B242" s="15" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C242" s="15" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Напряжение питания, В</t>
         </is>
       </c>
       <c r="D242" s="15" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="E242" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры дизельные</t>
+          <t>400</t>
         </is>
       </c>
       <c r="F242" s="17" t="n">
-        <v>1013</v>
+        <v>738</v>
       </c>
       <c r="G242" s="14" t="inlineStr">
         <is>
@@ -9005,21 +9005,21 @@
       </c>
       <c r="C243" s="15" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Точка росы, °C</t>
         </is>
       </c>
       <c r="D243" s="15" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>dewpt</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры масляные 2 ст.</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F243" s="17" t="n">
-        <v>987</v>
+        <v>600</v>
       </c>
       <c r="G243" s="14" t="inlineStr">
         <is>
@@ -9040,21 +9040,21 @@
       </c>
       <c r="C244" s="15" t="inlineStr">
         <is>
-          <t>Точка росы, °C</t>
+          <t>Товарная группа (1С)</t>
         </is>
       </c>
       <c r="D244" s="15" t="inlineStr">
         <is>
-          <t>dewpt</t>
+          <t>tgroup</t>
         </is>
       </c>
       <c r="E244" s="16" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>Компрессоры масляные 1 ст. (16-30 бар)</t>
         </is>
       </c>
       <c r="F244" s="17" t="n">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="G244" s="14" t="inlineStr">
         <is>
@@ -9085,11 +9085,11 @@
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры масляные 1 ст. (16-30 бар)</t>
+          <t>Компрессоры безмаслянные спиральные</t>
         </is>
       </c>
       <c r="F245" s="17" t="n">
-        <v>539</v>
+        <v>440</v>
       </c>
       <c r="G245" s="14" t="inlineStr">
         <is>
@@ -9120,11 +9120,11 @@
       </c>
       <c r="E246" s="16" t="inlineStr">
         <is>
-          <t>Компрессоры безмаслянные спиральные</t>
+          <t>Бустеры 40 бар</t>
         </is>
       </c>
       <c r="F246" s="17" t="n">
-        <v>440</v>
+        <v>247</v>
       </c>
       <c r="G246" s="14" t="inlineStr">
         <is>
@@ -9140,26 +9140,26 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>новый фасет</t>
+          <t>пробел в фасете</t>
         </is>
       </c>
       <c r="C247" s="15" t="inlineStr">
         <is>
-          <t>Товарная группа (1С)</t>
+          <t>Напряжение питания, В</t>
         </is>
       </c>
       <c r="D247" s="15" t="inlineStr">
         <is>
-          <t>tgroup</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Бустеры 40 бар</t>
+          <t>380/660</t>
         </is>
       </c>
       <c r="F247" s="17" t="n">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -20338,10 +20338,10 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>10879</v>
+        <v>9968</v>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
@@ -20392,10 +20392,10 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>20940</v>
+        <v>21851</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
